--- a/Report/Ramein_API_Test_Cases.xlsx
+++ b/Report/Ramein_API_Test_Cases.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SOFTWARE QUALITY ASSURANCE\project porto SQA\QA_RAMEIN_API_Automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SOFTWARE QUALITY ASSURANCE\project porto SQA\QA_RAMEIN_API_TESTING\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8AC0A6-BA88-43D4-AD47-852E8A92E506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC24E98-DDA0-4951-B78B-B8E31484C4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="4395" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="API Test Cases" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="396">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -1065,9 +1065,6 @@
     <t>Refresh with invalid refresh token</t>
   </si>
   <si>
-    <t>401/400</t>
-  </si>
-  <si>
     <t>Refresh rejected</t>
   </si>
   <si>
@@ -1203,10 +1200,16 @@
     <t>TC-API-102</t>
   </si>
   <si>
-    <t xml:space="preserve">false, harusnya event ga bisa di buat ini response nya 201 berhasil </t>
-  </si>
-  <si>
-    <t>Column1</t>
+    <t>Actual Status</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>PASSED</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1231,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1238,6 +1241,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF33"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1253,7 +1274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1261,12 +1282,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF66FF33"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1279,9 +1313,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="APITestCases" displayName="APITestCases" ref="A1:I103">
-  <autoFilter ref="A1:I103" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="APITestCases" displayName="APITestCases" ref="A1:J103">
+  <autoFilter ref="A1:J103" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Test Case ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Method"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Endpoint"/>
@@ -1290,7 +1324,8 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Preconditions / Test Data"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Expected Status"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Expected Result"/>
-    <tableColumn id="9" xr3:uid="{AE5CBC34-0F90-4CB3-B6BF-F98CF9EBC02B}" name="Column1"/>
+    <tableColumn id="9" xr3:uid="{AE5CBC34-0F90-4CB3-B6BF-F98CF9EBC02B}" name="Actual Status" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{09263D56-AE90-49ED-A351-1022E90BDFAC}" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1581,7 +1616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1592,9 +1627,10 @@
     <col min="6" max="6" width="45" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="59.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1619,11 +1655,14 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="J1" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1648,8 +1687,14 @@
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -1674,8 +1719,14 @@
       <c r="H3" s="2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
@@ -1700,8 +1751,14 @@
       <c r="H4" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -1726,8 +1783,14 @@
       <c r="H5" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>34</v>
       </c>
@@ -1752,8 +1815,14 @@
       <c r="H6" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
@@ -1778,8 +1847,14 @@
       <c r="H7" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>38</v>
       </c>
@@ -1804,8 +1879,14 @@
       <c r="H8" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>42</v>
       </c>
@@ -1830,8 +1911,14 @@
       <c r="H9" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>46</v>
       </c>
@@ -1856,8 +1943,14 @@
       <c r="H10" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
@@ -1882,8 +1975,14 @@
       <c r="H11" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>54</v>
       </c>
@@ -1908,8 +2007,14 @@
       <c r="H12" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J12" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>58</v>
       </c>
@@ -1934,8 +2039,14 @@
       <c r="H13" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>62</v>
       </c>
@@ -1960,8 +2071,14 @@
       <c r="H14" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>64</v>
       </c>
@@ -1986,8 +2103,14 @@
       <c r="H15" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>67</v>
       </c>
@@ -2012,8 +2135,14 @@
       <c r="H16" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>70</v>
       </c>
@@ -2038,8 +2167,14 @@
       <c r="H17" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>75</v>
       </c>
@@ -2064,8 +2199,14 @@
       <c r="H18" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>79</v>
       </c>
@@ -2090,8 +2231,14 @@
       <c r="H19" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>82</v>
       </c>
@@ -2116,8 +2263,14 @@
       <c r="H20" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>87</v>
       </c>
@@ -2142,8 +2295,14 @@
       <c r="H21" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>91</v>
       </c>
@@ -2168,8 +2327,14 @@
       <c r="H22" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>95</v>
       </c>
@@ -2194,8 +2359,14 @@
       <c r="H23" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>100</v>
       </c>
@@ -2220,8 +2391,14 @@
       <c r="H24" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>102</v>
       </c>
@@ -2246,8 +2423,14 @@
       <c r="H25" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>105</v>
       </c>
@@ -2272,8 +2455,14 @@
       <c r="H26" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>107</v>
       </c>
@@ -2298,8 +2487,14 @@
       <c r="H27" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>109</v>
       </c>
@@ -2324,8 +2519,14 @@
       <c r="H28" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>112</v>
       </c>
@@ -2350,8 +2551,14 @@
       <c r="H29" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>114</v>
       </c>
@@ -2376,8 +2583,14 @@
       <c r="H30" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>116</v>
       </c>
@@ -2402,8 +2615,14 @@
       <c r="H31" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>118</v>
       </c>
@@ -2428,8 +2647,14 @@
       <c r="H32" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>120</v>
       </c>
@@ -2454,8 +2679,14 @@
       <c r="H33" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>122</v>
       </c>
@@ -2480,8 +2711,14 @@
       <c r="H34" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>124</v>
       </c>
@@ -2506,8 +2743,14 @@
       <c r="H35" s="2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>127</v>
       </c>
@@ -2532,8 +2775,14 @@
       <c r="H36" s="2" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>130</v>
       </c>
@@ -2558,8 +2807,14 @@
       <c r="H37" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>133</v>
       </c>
@@ -2584,8 +2839,14 @@
       <c r="H38" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>136</v>
       </c>
@@ -2610,11 +2871,14 @@
       <c r="H39" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" s="6" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>139</v>
       </c>
@@ -2639,8 +2903,14 @@
       <c r="H40" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>143</v>
       </c>
@@ -2665,8 +2935,14 @@
       <c r="H41" s="2" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I41" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>148</v>
       </c>
@@ -2691,8 +2967,14 @@
       <c r="H42" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I42" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>152</v>
       </c>
@@ -2700,7 +2982,7 @@
         <v>9</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>11</v>
@@ -2717,8 +2999,14 @@
       <c r="H43" s="2" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I43" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>157</v>
       </c>
@@ -2726,7 +3014,7 @@
         <v>9</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>24</v>
@@ -2738,13 +3026,19 @@
         <v>159</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I44" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>160</v>
       </c>
@@ -2752,7 +3046,7 @@
         <v>9</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>24</v>
@@ -2769,8 +3063,14 @@
       <c r="H45" s="2" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I45" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>165</v>
       </c>
@@ -2795,8 +3095,14 @@
       <c r="H46" s="2" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>170</v>
       </c>
@@ -2821,8 +3127,14 @@
       <c r="H47" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I47" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>172</v>
       </c>
@@ -2847,8 +3159,14 @@
       <c r="H48" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>174</v>
       </c>
@@ -2873,8 +3191,14 @@
       <c r="H49" s="2" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I49" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>178</v>
       </c>
@@ -2899,8 +3223,14 @@
       <c r="H50" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I50" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>180</v>
       </c>
@@ -2925,8 +3255,14 @@
       <c r="H51" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I51" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>182</v>
       </c>
@@ -2951,8 +3287,14 @@
       <c r="H52" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I52" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>185</v>
       </c>
@@ -2977,8 +3319,14 @@
       <c r="H53" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I53" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>187</v>
       </c>
@@ -3003,8 +3351,14 @@
       <c r="H54" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I54" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>191</v>
       </c>
@@ -3029,8 +3383,14 @@
       <c r="H55" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I55" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>193</v>
       </c>
@@ -3055,8 +3415,14 @@
       <c r="H56" s="2" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I56" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>197</v>
       </c>
@@ -3081,8 +3447,14 @@
       <c r="H57" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I57" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>199</v>
       </c>
@@ -3096,19 +3468,25 @@
         <v>11</v>
       </c>
       <c r="E58" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="G58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" t="s">
         <v>390</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H58" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I58" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>204</v>
       </c>
@@ -3133,8 +3511,14 @@
       <c r="H59" s="2" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I59" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>208</v>
       </c>
@@ -3159,8 +3543,14 @@
       <c r="H60" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I60" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>210</v>
       </c>
@@ -3185,8 +3575,14 @@
       <c r="H61" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I61" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>215</v>
       </c>
@@ -3211,8 +3607,14 @@
       <c r="H62" s="2" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>217</v>
       </c>
@@ -3237,8 +3639,14 @@
       <c r="H63" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I63" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>221</v>
       </c>
@@ -3263,8 +3671,14 @@
       <c r="H64" s="2" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I64" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>224</v>
       </c>
@@ -3289,8 +3703,14 @@
       <c r="H65" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I65" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>226</v>
       </c>
@@ -3315,8 +3735,14 @@
       <c r="H66" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I66" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>230</v>
       </c>
@@ -3324,7 +3750,7 @@
         <v>9</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>11</v>
@@ -3341,8 +3767,14 @@
       <c r="H67" s="2" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I67" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>235</v>
       </c>
@@ -3367,8 +3799,14 @@
       <c r="H68" s="2" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I68" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>238</v>
       </c>
@@ -3393,8 +3831,14 @@
       <c r="H69" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I69" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>242</v>
       </c>
@@ -3419,8 +3863,14 @@
       <c r="H70" s="2" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I70" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J70" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>247</v>
       </c>
@@ -3445,8 +3895,14 @@
       <c r="H71" s="2" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>249</v>
       </c>
@@ -3471,8 +3927,14 @@
       <c r="H72" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I72" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J72" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>251</v>
       </c>
@@ -3497,8 +3959,14 @@
       <c r="H73" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I73" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>254</v>
       </c>
@@ -3523,8 +3991,14 @@
       <c r="H74" s="2" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I74" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J74" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>258</v>
       </c>
@@ -3549,8 +4023,14 @@
       <c r="H75" s="2" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I75" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J75" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>260</v>
       </c>
@@ -3575,8 +4055,14 @@
       <c r="H76" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I76" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>264</v>
       </c>
@@ -3601,8 +4087,14 @@
       <c r="H77" s="2" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I77" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J77" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>266</v>
       </c>
@@ -3627,8 +4119,14 @@
       <c r="H78" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I78" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J78" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>271</v>
       </c>
@@ -3653,8 +4151,14 @@
       <c r="H79" s="2" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I79" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>273</v>
       </c>
@@ -3679,8 +4183,14 @@
       <c r="H80" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I80" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>276</v>
       </c>
@@ -3705,8 +4215,14 @@
       <c r="H81" s="2" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I81" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J81" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>279</v>
       </c>
@@ -3731,8 +4247,14 @@
       <c r="H82" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I82" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="J82" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>283</v>
       </c>
@@ -3757,8 +4279,14 @@
       <c r="H83" s="2" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I83" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J83" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>287</v>
       </c>
@@ -3783,8 +4311,14 @@
       <c r="H84" s="2" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I84" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J84" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>292</v>
       </c>
@@ -3809,8 +4343,14 @@
       <c r="H85" s="2" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I85" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>297</v>
       </c>
@@ -3835,8 +4375,14 @@
       <c r="H86" s="2" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I86" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>302</v>
       </c>
@@ -3861,8 +4407,14 @@
       <c r="H87" s="2" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I87" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J87" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>304</v>
       </c>
@@ -3887,8 +4439,14 @@
       <c r="H88" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I88" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>307</v>
       </c>
@@ -3913,8 +4471,14 @@
       <c r="H89" s="2" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J89" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>309</v>
       </c>
@@ -3939,8 +4503,14 @@
       <c r="H90" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I90" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J90" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>311</v>
       </c>
@@ -3965,8 +4535,14 @@
       <c r="H91" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I91" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J91" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>316</v>
       </c>
@@ -3991,8 +4567,14 @@
       <c r="H92" s="2" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>319</v>
       </c>
@@ -4017,8 +4599,14 @@
       <c r="H93" s="2" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I93" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J93" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>322</v>
       </c>
@@ -4043,8 +4631,14 @@
       <c r="H94" s="2" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I94" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J94" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>325</v>
       </c>
@@ -4069,8 +4663,14 @@
       <c r="H95" s="2" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I95" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J95" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>329</v>
       </c>
@@ -4095,8 +4695,14 @@
       <c r="H96" s="2" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I96" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J96" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>332</v>
       </c>
@@ -4121,8 +4727,14 @@
       <c r="H97" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I97" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J97" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>337</v>
       </c>
@@ -4147,8 +4759,14 @@
       <c r="H98" s="2" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I98" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J98" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>340</v>
       </c>
@@ -4173,8 +4791,14 @@
       <c r="H99" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I99" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J99" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>345</v>
       </c>
@@ -4199,10 +4823,16 @@
       <c r="H100" s="2" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I100" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J100" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>17</v>
@@ -4220,27 +4850,33 @@
         <v>81</v>
       </c>
       <c r="G101" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H101" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="H101" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I101" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J101" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>85</v>
@@ -4249,33 +4885,45 @@
         <v>14</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+        <v>351</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J102" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C103" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D103" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E103" s="2" t="s">
+      <c r="F103" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="F103" s="2" t="s">
+      <c r="G103" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H103" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="G103" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>357</v>
+      <c r="I103" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J103" s="5" t="s">
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -4297,21 +4945,21 @@
   <sheetData>
     <row r="1" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B3" s="2">
         <v>101</v>
@@ -4319,7 +4967,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B4" s="2">
         <v>34</v>
@@ -4327,7 +4975,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B5" s="2">
         <v>67</v>
@@ -4335,18 +4983,18 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -4367,7 +5015,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4376,10 +5024,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -4393,7 +5041,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>85</v>
@@ -4410,7 +5058,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>85</v>
@@ -4427,7 +5075,7 @@
         <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>52</v>
@@ -4444,7 +5092,7 @@
         <v>71</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>104</v>
@@ -4461,7 +5109,7 @@
         <v>83</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>85</v>
@@ -4478,7 +5126,7 @@
         <v>88</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>85</v>
@@ -4495,7 +5143,7 @@
         <v>92</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>85</v>
@@ -4512,10 +5160,10 @@
         <v>96</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -4529,10 +5177,10 @@
         <v>153</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -4546,10 +5194,10 @@
         <v>166</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -4563,7 +5211,7 @@
         <v>188</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>104</v>
@@ -4580,10 +5228,10 @@
         <v>194</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>386</v>
       </c>
     </row>
   </sheetData>
